--- a/linked_data.xlsx
+++ b/linked_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phamn\Documents\Project\Rebound Classes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9FE6F4D-A518-4E00-97BB-8CE17131D36C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0D44100-5F76-40A4-BD50-96DB7ACE30CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -220,12 +220,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -531,9 +530,14 @@
   <dimension ref="A1:T9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
+    <col min="4" max="4" width="21.36328125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.08984375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="26.90625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="27" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="25.54296875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="114.08984375" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="46.08984375" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="51.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.35">
@@ -599,494 +603,492 @@
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A2" s="2">
+      <c r="A2">
         <v>47834250</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="2">
+      <c r="D2">
         <v>0</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2">
         <v>0</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" t="s">
         <v>22</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" t="s">
         <v>22</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="P2" s="2" t="s">
+      <c r="I2" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" t="s">
+        <v>23</v>
+      </c>
+      <c r="K2" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O2" t="s">
+        <v>24</v>
+      </c>
+      <c r="P2" t="s">
         <v>25</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="Q2" t="s">
         <v>26</v>
       </c>
-      <c r="R2" s="2"/>
-      <c r="S2" s="2" t="s">
+      <c r="S2" t="s">
         <v>27</v>
       </c>
-      <c r="T2" s="2"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A3" s="2">
+      <c r="A3">
         <v>47123427</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="2">
+      <c r="D3">
         <v>0</v>
       </c>
-      <c r="E3" s="2">
+      <c r="E3">
         <v>0</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" t="s">
         <v>28</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q3" s="2" t="s">
+      <c r="H3" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J3" t="s">
+        <v>23</v>
+      </c>
+      <c r="K3" t="s">
+        <v>29</v>
+      </c>
+      <c r="L3" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3" t="s">
+        <v>29</v>
+      </c>
+      <c r="N3" t="s">
+        <v>24</v>
+      </c>
+      <c r="O3" t="s">
+        <v>29</v>
+      </c>
+      <c r="P3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q3" t="s">
         <v>30</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="R3" t="s">
         <v>31</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="S3" t="s">
         <v>32</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="T3" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A4" s="2">
+      <c r="A4">
         <v>49011022</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="2">
+      <c r="D4">
         <v>1</v>
       </c>
-      <c r="E4" s="2">
+      <c r="E4">
         <v>0</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="F4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" t="s">
         <v>22</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" t="s">
         <v>28</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" t="s">
         <v>22</v>
       </c>
-      <c r="K4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N4" s="2" t="s">
+      <c r="K4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L4" t="s">
+        <v>29</v>
+      </c>
+      <c r="M4" t="s">
+        <v>24</v>
+      </c>
+      <c r="N4" t="s">
         <v>25</v>
       </c>
-      <c r="O4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q4" s="2" t="s">
+      <c r="O4" t="s">
+        <v>24</v>
+      </c>
+      <c r="P4" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q4" t="s">
         <v>35</v>
       </c>
-      <c r="R4" s="2" t="s">
+      <c r="R4" t="s">
         <v>36</v>
       </c>
-      <c r="S4" s="2" t="s">
+      <c r="S4" t="s">
         <v>37</v>
       </c>
-      <c r="T4" s="2" t="s">
+      <c r="T4" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A5" s="2">
+      <c r="A5">
         <v>49004999</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" t="s">
         <v>34</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" t="s">
         <v>39</v>
       </c>
-      <c r="D5" s="2">
+      <c r="D5">
         <v>1</v>
       </c>
-      <c r="E5" s="2">
+      <c r="E5">
         <v>0</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G5" s="2" t="s">
+      <c r="F5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" t="s">
         <v>22</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q5" s="2" t="s">
+      <c r="H5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I5" t="s">
+        <v>23</v>
+      </c>
+      <c r="J5" t="s">
+        <v>23</v>
+      </c>
+      <c r="K5" t="s">
+        <v>29</v>
+      </c>
+      <c r="L5" t="s">
+        <v>29</v>
+      </c>
+      <c r="M5" t="s">
+        <v>24</v>
+      </c>
+      <c r="N5" t="s">
+        <v>24</v>
+      </c>
+      <c r="O5" t="s">
+        <v>29</v>
+      </c>
+      <c r="P5" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q5" t="s">
         <v>40</v>
       </c>
-      <c r="R5" s="2" t="s">
+      <c r="R5" t="s">
         <v>41</v>
       </c>
-      <c r="S5" s="2" t="s">
+      <c r="S5" t="s">
         <v>42</v>
       </c>
-      <c r="T5" s="2" t="s">
+      <c r="T5" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A6" s="2">
+      <c r="A6">
         <v>49004999</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" t="s">
         <v>39</v>
       </c>
-      <c r="D6" s="2">
+      <c r="D6">
         <v>1</v>
       </c>
-      <c r="E6" s="2">
+      <c r="E6">
         <v>0</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q6" s="2" t="s">
+      <c r="F6" t="s">
+        <v>23</v>
+      </c>
+      <c r="G6" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" t="s">
+        <v>23</v>
+      </c>
+      <c r="I6" t="s">
+        <v>23</v>
+      </c>
+      <c r="J6" t="s">
+        <v>23</v>
+      </c>
+      <c r="K6" t="s">
+        <v>29</v>
+      </c>
+      <c r="L6" t="s">
+        <v>29</v>
+      </c>
+      <c r="M6" t="s">
+        <v>29</v>
+      </c>
+      <c r="N6" t="s">
+        <v>24</v>
+      </c>
+      <c r="O6" t="s">
+        <v>29</v>
+      </c>
+      <c r="P6" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q6" t="s">
         <v>44</v>
       </c>
-      <c r="R6" s="2" t="s">
+      <c r="R6" t="s">
         <v>45</v>
       </c>
-      <c r="S6" s="2" t="s">
+      <c r="S6" t="s">
         <v>42</v>
       </c>
-      <c r="T6" s="2" t="s">
+      <c r="T6" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A7" s="2">
+      <c r="A7">
         <v>49004999</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" t="s">
         <v>21</v>
       </c>
-      <c r="D7" s="2">
+      <c r="D7">
         <v>1</v>
       </c>
-      <c r="E7" s="2">
+      <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G7" s="2" t="s">
+      <c r="F7" t="s">
+        <v>23</v>
+      </c>
+      <c r="G7" t="s">
         <v>22</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q7" s="2" t="s">
+      <c r="H7" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" t="s">
+        <v>23</v>
+      </c>
+      <c r="J7" t="s">
+        <v>23</v>
+      </c>
+      <c r="K7" t="s">
+        <v>29</v>
+      </c>
+      <c r="L7" t="s">
+        <v>29</v>
+      </c>
+      <c r="M7" t="s">
+        <v>24</v>
+      </c>
+      <c r="N7" t="s">
+        <v>24</v>
+      </c>
+      <c r="O7" t="s">
+        <v>24</v>
+      </c>
+      <c r="P7" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q7" t="s">
         <v>40</v>
       </c>
-      <c r="R7" s="2" t="s">
+      <c r="R7" t="s">
         <v>41</v>
       </c>
-      <c r="S7" s="2" t="s">
+      <c r="S7" t="s">
         <v>46</v>
       </c>
-      <c r="T7" s="2" t="s">
+      <c r="T7" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A8" s="2">
+      <c r="A8">
         <v>48665541</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" t="s">
         <v>39</v>
       </c>
-      <c r="D8" s="2">
+      <c r="D8">
         <v>1</v>
       </c>
-      <c r="E8" s="2">
+      <c r="E8">
         <v>0</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" s="2" t="s">
+      <c r="F8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" t="s">
         <v>48</v>
       </c>
-      <c r="I8" s="2" t="s">
+      <c r="I8" t="s">
         <v>48</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="J8" t="s">
         <v>48</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q8" s="2" t="s">
+      <c r="K8" t="s">
+        <v>29</v>
+      </c>
+      <c r="L8" t="s">
+        <v>29</v>
+      </c>
+      <c r="M8" t="s">
+        <v>29</v>
+      </c>
+      <c r="N8" t="s">
+        <v>29</v>
+      </c>
+      <c r="O8" t="s">
+        <v>29</v>
+      </c>
+      <c r="P8" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q8" t="s">
         <v>49</v>
       </c>
-      <c r="R8" s="2" t="s">
+      <c r="R8" t="s">
         <v>50</v>
       </c>
-      <c r="S8" s="2" t="s">
+      <c r="S8" t="s">
         <v>49</v>
       </c>
-      <c r="T8" s="2" t="s">
+      <c r="T8" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A9" s="2">
+      <c r="A9">
         <v>49004999</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" t="s">
         <v>34</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="2">
+      <c r="D9">
         <v>1</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9">
         <v>0</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q9" s="2" t="s">
+      <c r="F9" t="s">
+        <v>23</v>
+      </c>
+      <c r="G9" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" t="s">
+        <v>23</v>
+      </c>
+      <c r="I9" t="s">
+        <v>23</v>
+      </c>
+      <c r="J9" t="s">
+        <v>23</v>
+      </c>
+      <c r="K9" t="s">
+        <v>29</v>
+      </c>
+      <c r="L9" t="s">
+        <v>29</v>
+      </c>
+      <c r="M9" t="s">
+        <v>29</v>
+      </c>
+      <c r="N9" t="s">
+        <v>24</v>
+      </c>
+      <c r="O9" t="s">
+        <v>24</v>
+      </c>
+      <c r="P9" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q9" t="s">
         <v>44</v>
       </c>
-      <c r="R9" s="2" t="s">
+      <c r="R9" t="s">
         <v>45</v>
       </c>
-      <c r="S9" s="2" t="s">
+      <c r="S9" t="s">
         <v>46</v>
       </c>
-      <c r="T9" s="2" t="s">
+      <c r="T9" t="s">
         <v>47</v>
       </c>
     </row>

--- a/linked_data.xlsx
+++ b/linked_data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phamn\Documents\Project\Rebound Classes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0D44100-5F76-40A4-BD50-96DB7ACE30CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66B26F09-CEBA-46C3-8DB7-8186586D4340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,15 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="50">
   <si>
     <t>StudentID</t>
   </si>
   <si>
     <t>Session</t>
-  </si>
-  <si>
-    <t>Unit_Exit</t>
   </si>
   <si>
     <t>First Generation Student</t>
@@ -146,12 +143,6 @@
     <t>COMP1000- Introduction to Computer Programming</t>
   </si>
   <si>
-    <t>I want to enhance the concepts that I still do not understand, so that I attend the REBOUND classes to improve my mastery of the topic that I do not understand.</t>
-  </si>
-  <si>
-    <t>Provides examples and the method to solve problems.</t>
-  </si>
-  <si>
     <t>Concept explanation</t>
   </si>
   <si>
@@ -180,6 +171,9 @@
   </si>
   <si>
     <t>keep this teacher</t>
+  </si>
+  <si>
+    <t>Unit</t>
   </si>
 </sst>
 </file>
@@ -527,20 +521,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:T7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="21.36328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="26.90625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="25.54296875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="114.08984375" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="46.08984375" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="51.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="55.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="29" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="29.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="27.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="28.140625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="22.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="33.85546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="138.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="114.140625" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="46.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="51.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -548,69 +548,69 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="Q1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="s">
+      <c r="R1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="1" t="s">
-        <v>19</v>
-      </c>
     </row>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>47834250</v>
       </c>
       <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
         <v>20</v>
-      </c>
-      <c r="C2" t="s">
-        <v>21</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -619,54 +619,54 @@
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O2" t="s">
+        <v>23</v>
+      </c>
+      <c r="P2" t="s">
         <v>24</v>
       </c>
-      <c r="L2" t="s">
-        <v>24</v>
-      </c>
-      <c r="M2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N2" t="s">
-        <v>24</v>
-      </c>
-      <c r="O2" t="s">
-        <v>24</v>
-      </c>
-      <c r="P2" t="s">
+      <c r="Q2" t="s">
         <v>25</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="S2" t="s">
         <v>26</v>
       </c>
-      <c r="S2" t="s">
-        <v>27</v>
-      </c>
     </row>
-    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>47123427</v>
       </c>
       <c r="B3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C3" t="s">
         <v>20</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -675,60 +675,60 @@
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K3" t="s">
+        <v>28</v>
+      </c>
+      <c r="L3" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3" t="s">
+        <v>28</v>
+      </c>
+      <c r="N3" t="s">
+        <v>23</v>
+      </c>
+      <c r="O3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P3" t="s">
+        <v>23</v>
+      </c>
+      <c r="Q3" t="s">
         <v>29</v>
       </c>
-      <c r="L3" t="s">
-        <v>29</v>
-      </c>
-      <c r="M3" t="s">
-        <v>29</v>
-      </c>
-      <c r="N3" t="s">
-        <v>24</v>
-      </c>
-      <c r="O3" t="s">
-        <v>29</v>
-      </c>
-      <c r="P3" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q3" t="s">
+      <c r="R3" t="s">
         <v>30</v>
       </c>
-      <c r="R3" t="s">
+      <c r="S3" t="s">
         <v>31</v>
       </c>
-      <c r="S3" t="s">
+      <c r="T3" t="s">
         <v>32</v>
       </c>
-      <c r="T3" t="s">
-        <v>33</v>
-      </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>49011022</v>
       </c>
       <c r="B4" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -737,60 +737,60 @@
         <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M4" t="s">
+        <v>23</v>
+      </c>
+      <c r="N4" t="s">
         <v>24</v>
       </c>
-      <c r="N4" t="s">
-        <v>25</v>
-      </c>
       <c r="O4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q4" t="s">
+        <v>34</v>
+      </c>
+      <c r="R4" t="s">
         <v>35</v>
       </c>
-      <c r="R4" t="s">
+      <c r="S4" t="s">
         <v>36</v>
       </c>
-      <c r="S4" t="s">
+      <c r="T4" t="s">
         <v>37</v>
       </c>
-      <c r="T4" t="s">
-        <v>38</v>
-      </c>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>49004999</v>
       </c>
       <c r="B5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -799,60 +799,60 @@
         <v>0</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G5" t="s">
         <v>22</v>
       </c>
       <c r="H5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M5" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="N5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q5" t="s">
+        <v>41</v>
+      </c>
+      <c r="R5" t="s">
+        <v>42</v>
+      </c>
+      <c r="S5" t="s">
+        <v>39</v>
+      </c>
+      <c r="T5" t="s">
         <v>40</v>
       </c>
-      <c r="R5" t="s">
-        <v>41</v>
-      </c>
-      <c r="S5" t="s">
-        <v>42</v>
-      </c>
-      <c r="T5" t="s">
-        <v>43</v>
-      </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>49004999</v>
+        <v>48665541</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -861,60 +861,60 @@
         <v>0</v>
       </c>
       <c r="F6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H6" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="I6" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="J6" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="K6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="N6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="O6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P6" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="Q6" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="R6" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="S6" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="T6" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>49004999</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D7">
         <v>1</v>
@@ -923,173 +923,49 @@
         <v>0</v>
       </c>
       <c r="F7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G7" t="s">
         <v>22</v>
       </c>
       <c r="H7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="L7" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="M7" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="N7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Q7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="R7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="S7" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="T7" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A8">
-        <v>48665541</v>
-      </c>
-      <c r="B8" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <v>0</v>
-      </c>
-      <c r="F8" t="s">
-        <v>23</v>
-      </c>
-      <c r="G8" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" t="s">
-        <v>48</v>
-      </c>
-      <c r="I8" t="s">
-        <v>48</v>
-      </c>
-      <c r="J8" t="s">
-        <v>48</v>
-      </c>
-      <c r="K8" t="s">
-        <v>29</v>
-      </c>
-      <c r="L8" t="s">
-        <v>29</v>
-      </c>
-      <c r="M8" t="s">
-        <v>29</v>
-      </c>
-      <c r="N8" t="s">
-        <v>29</v>
-      </c>
-      <c r="O8" t="s">
-        <v>29</v>
-      </c>
-      <c r="P8" t="s">
-        <v>29</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>49</v>
-      </c>
-      <c r="R8" t="s">
-        <v>50</v>
-      </c>
-      <c r="S8" t="s">
-        <v>49</v>
-      </c>
-      <c r="T8" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A9">
-        <v>49004999</v>
-      </c>
-      <c r="B9" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>0</v>
-      </c>
-      <c r="F9" t="s">
-        <v>23</v>
-      </c>
-      <c r="G9" t="s">
-        <v>23</v>
-      </c>
-      <c r="H9" t="s">
-        <v>23</v>
-      </c>
-      <c r="I9" t="s">
-        <v>23</v>
-      </c>
-      <c r="J9" t="s">
-        <v>23</v>
-      </c>
-      <c r="K9" t="s">
-        <v>29</v>
-      </c>
-      <c r="L9" t="s">
-        <v>29</v>
-      </c>
-      <c r="M9" t="s">
-        <v>29</v>
-      </c>
-      <c r="N9" t="s">
-        <v>24</v>
-      </c>
-      <c r="O9" t="s">
-        <v>24</v>
-      </c>
-      <c r="P9" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q9" t="s">
         <v>44</v>
-      </c>
-      <c r="R9" t="s">
-        <v>45</v>
-      </c>
-      <c r="S9" t="s">
-        <v>46</v>
-      </c>
-      <c r="T9" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
